--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T06:35:39+00:00</t>
+    <t>2026-03-30T12:50:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="179">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:50:33+00:00</t>
+    <t>2026-04-02T10:32:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -364,6 +364,10 @@
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>erp-tprescription-carbon-copy-logical.rxVerordnung.bezeichnung</t>
@@ -1720,7 +1724,7 @@
         <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>105</v>
@@ -1728,10 +1732,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1754,13 +1758,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1811,7 +1815,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1828,10 +1832,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1854,13 +1858,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1911,7 +1915,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1928,10 +1932,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1954,13 +1958,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2011,7 +2015,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2028,10 +2032,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2054,13 +2058,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2111,7 +2115,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2128,10 +2132,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2154,13 +2158,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2211,7 +2215,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2228,10 +2232,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2257,10 +2261,10 @@
         <v>91</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2311,7 +2315,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -2328,10 +2332,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2357,10 +2361,10 @@
         <v>87</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2411,7 +2415,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -2428,10 +2432,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2528,10 +2532,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2630,10 +2634,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2726,7 +2730,7 @@
         <v>75</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>105</v>
@@ -2734,10 +2738,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2760,13 +2764,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2817,7 +2821,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -2834,10 +2838,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2860,13 +2864,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2917,7 +2921,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2934,10 +2938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2960,13 +2964,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3017,7 +3021,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3034,10 +3038,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3060,13 +3064,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3117,7 +3121,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3134,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3160,13 +3164,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3217,7 +3221,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3234,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3263,10 +3267,10 @@
         <v>87</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3317,7 +3321,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3334,10 +3338,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3434,10 +3438,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3536,10 +3540,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3632,7 +3636,7 @@
         <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>105</v>
@@ -3640,10 +3644,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3666,13 +3670,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3723,7 +3727,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -3740,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3766,13 +3770,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3823,7 +3827,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3840,10 +3844,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3869,10 +3873,10 @@
         <v>91</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3923,7 +3927,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3940,10 +3944,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3966,13 +3970,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4023,7 +4027,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4040,10 +4044,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4066,13 +4070,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4123,7 +4127,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4140,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4166,13 +4170,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4223,7 +4227,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -4240,10 +4244,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4269,10 +4273,10 @@
         <v>87</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4323,7 +4327,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -4340,10 +4344,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4440,10 +4444,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4542,10 +4546,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4638,7 +4642,7 @@
         <v>75</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -4646,10 +4650,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4675,10 +4679,10 @@
         <v>91</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4729,7 +4733,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -4746,10 +4750,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4775,10 +4779,10 @@
         <v>91</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4829,7 +4833,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4846,10 +4850,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4872,13 +4876,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4929,7 +4933,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -4946,10 +4950,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -4972,13 +4976,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5029,7 +5033,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T10:32:58+00:00</t>
+    <t>2026-04-02T10:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T10:59:26+00:00</t>
+    <t>2026-04-02T12:19:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="178">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:19:32+00:00</t>
+    <t>2026-04-10T07:54:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -364,10 +364,6 @@
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>erp-tprescription-carbon-copy-logical.rxVerordnung.bezeichnung</t>
@@ -1724,7 +1720,7 @@
         <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>105</v>
@@ -1732,10 +1728,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1758,13 +1754,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="M9" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1815,7 +1811,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1832,10 +1828,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1858,13 +1854,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L10" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="M10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1915,7 +1911,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1932,10 +1928,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1958,13 +1954,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>122</v>
-      </c>
       <c r="M11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2015,7 +2011,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2032,10 +2028,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2058,13 +2054,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2115,7 +2111,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2132,10 +2128,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2158,13 +2154,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>127</v>
-      </c>
       <c r="M13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2215,7 +2211,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2232,10 +2228,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2261,10 +2257,10 @@
         <v>91</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2315,7 +2311,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -2332,10 +2328,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2361,10 +2357,10 @@
         <v>87</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2415,7 +2411,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -2432,10 +2428,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2532,10 +2528,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2634,10 +2630,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2730,7 +2726,7 @@
         <v>75</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>105</v>
@@ -2738,10 +2734,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2764,13 +2760,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>137</v>
-      </c>
       <c r="M19" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2821,7 +2817,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -2838,10 +2834,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2864,13 +2860,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2921,7 +2917,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2938,10 +2934,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2964,13 +2960,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3021,7 +3017,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3038,10 +3034,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3064,13 +3060,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3121,7 +3117,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3138,10 +3134,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3164,13 +3160,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3221,7 +3217,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3238,10 +3234,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3267,10 +3263,10 @@
         <v>87</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3321,7 +3317,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3338,10 +3334,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3438,10 +3434,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3540,10 +3536,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3636,7 +3632,7 @@
         <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>105</v>
@@ -3644,10 +3640,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3670,13 +3666,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3727,7 +3723,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -3744,10 +3740,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3770,13 +3766,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3827,7 +3823,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3844,10 +3840,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3873,10 +3869,10 @@
         <v>91</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3927,7 +3923,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3944,10 +3940,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3970,13 +3966,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4027,7 +4023,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4044,10 +4040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4070,13 +4066,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4127,7 +4123,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4144,10 +4140,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4170,13 +4166,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="M33" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4227,7 +4223,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -4244,10 +4240,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4273,10 +4269,10 @@
         <v>87</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4327,7 +4323,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -4344,10 +4340,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4444,10 +4440,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4546,10 +4542,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4642,7 +4638,7 @@
         <v>75</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -4650,10 +4646,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4679,10 +4675,10 @@
         <v>91</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4733,7 +4729,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -4750,10 +4746,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4779,10 +4775,10 @@
         <v>91</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4833,7 +4829,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4850,10 +4846,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4876,13 +4872,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L40" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="M40" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4933,7 +4929,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -4950,10 +4946,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -4976,13 +4972,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L41" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="M41" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5033,7 +5029,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T07:54:58+00:00</t>
+    <t>2026-04-13T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:15:24+00:00</t>
+    <t>2026-04-14T04:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
